--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ARIZONA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/ARIZONA_2014.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C120">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C269">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C279">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="B656" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C656">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C708">
@@ -18834,7 +18834,7 @@
       </c>
       <c r="B1027" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C1027">
@@ -20364,7 +20364,7 @@
       </c>
       <c r="B1112" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1112">
